--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/OKLAHOMA_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/OKLAHOMA_2024.xlsx
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C180">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C217">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C324">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C676">
